--- a/partner_results/chmo/ClassMissingGermanDefinition_chmo.xlsx
+++ b/partner_results/chmo/ClassMissingGermanDefinition_chmo.xlsx
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>laser-induced breakdown spectroscopy [chmo]</t>
+          <t>sensor [chmo]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A type of atomic emission spectrometry where a high energy laser pulse is used to generate a plasma which acts as the excitation source.</t>
+          <t>A piece of apparatus that is used to measure a physical quantity.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mixing [chmo]</t>
+          <t>concentration output [chmo]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>planned process</t>
+          <t>measurement metadata</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The combining of components, particles or layers into a more homogeneous state. The mixing may be achieved manually or mechanically by shifting the material with stirrers or pumps or by revolving or shaking the container. The process μst not permit segregation of particles of different size or properties. Homogeneity may be considered to have been achieved in a practical sense when the sampling error of the processed portion is negligible compared to the total error of the measurement system. [ https://doi.org/10.1351/goldbook.M03945 ]</t>
+          <t>Experimental method output expressing the contribution of one constituent to the composition of a mixture. (chmo defined)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -484,7 +484,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>extrusion [chmo]</t>
+          <t>mixing [chmo]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,7 +495,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A process used to create objects of a fixed cross-sectional profile by forcing or drawing a material through a die.</t>
+          <t>The combining of components, particles or layers into a more homogeneous state. The mixing may be achieved manually or mechanically by shifting the material with stirrers or pumps or by revolving or shaking the container. The process μst not permit segregation of particles of different size or properties. Homogeneity may be considered to have been achieved in a practical sense when the sampling error of the processed portion is negligible compared to the total error of the measurement system. [ https://doi.org/10.1351/goldbook.M03945 ]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -503,18 +503,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sensor [chmo]</t>
+          <t>extrusion [chmo]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>planned process</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A piece of apparatus that is used to measure a physical quantity.</t>
+          <t>A process used to create objects of a fixed cross-sectional profile by forcing or drawing a material through a die.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -522,18 +522,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>concentration output [chmo]</t>
+          <t>laser-induced breakdown spectroscopy [chmo]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>measurement metadata</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Experimental method output expressing the contribution of one constituent to the composition of a mixture. (chmo defined)</t>
+          <t>A type of atomic emission spectrometry where a high energy laser pulse is used to generate a plasma which acts as the excitation source.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
